--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +820,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +840,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +883,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +944,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1079,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1204,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1971,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,7 +2015,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2002,35 +2026,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2087,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2106,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2142,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2203,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2222,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2258,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2319,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2338,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2363,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2439,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2483,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2494,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2507,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2555,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,69 +2610,65 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2666,7 +2690,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2676,17 +2700,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2720,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2792,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2908,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2958,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3019,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3038,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3074,3255 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD50"/>
+  <dimension ref="A1:AD68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -835,14 +835,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -850,7 +850,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -893,24 +893,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1007,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1040,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1064,17 +1068,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1084,13 +1088,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1133,24 +1141,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1160,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1199,22 +1207,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1280,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1379,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1440,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1551,7 +1575,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1562,7 +1586,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1702,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1768,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1794,7 +1818,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1934,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2000,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2026,7 +2050,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2116,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2142,7 +2166,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2232,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2258,7 +2282,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2348,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2373,12 +2397,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2415,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2468,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2482,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,41 +2512,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2555,12 +2583,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2602,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2599,46 +2627,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2671,12 +2703,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2722,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2747,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2823,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2842,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2842,35 +2878,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2939,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2958,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +2983,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3019,12 +3059,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3078,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,46 +3103,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3179,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3198,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,7 +3223,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3190,7 +3234,7 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3247,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3213,7 +3257,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3223,40 +3267,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3318,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3280,17 +3328,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3300,13 +3348,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/23</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3371,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3329,7 +3381,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3367,12 +3419,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3438,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3422,7 +3474,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -3435,22 +3487,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3483,12 +3535,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3554,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3538,7 +3590,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -3551,22 +3603,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3599,12 +3651,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3670,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3654,7 +3706,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3719,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3677,7 +3729,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3715,12 +3767,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3734,7 +3786,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3770,7 +3822,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3835,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3793,7 +3845,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3831,12 +3883,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3902,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3886,7 +3938,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -3899,22 +3951,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3947,12 +3999,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3966,7 +4018,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4054,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4067,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4063,12 +4115,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4134,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4170,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4183,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4141,7 +4193,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4184,7 +4236,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4250,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,7 +4286,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4299,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4257,7 +4309,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4295,12 +4347,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4366,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,7 +4402,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4415,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4373,7 +4425,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4411,12 +4463,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4482,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,7 +4518,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4531,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4489,7 +4541,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4527,12 +4579,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4598,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,35 +4634,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4643,12 +4695,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4714,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4687,7 +4739,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4698,35 +4750,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4759,12 +4811,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4830,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,35 +4866,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4875,12 +4927,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4894,7 +4946,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4930,35 +4982,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5043,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5062,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5098,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5159,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5178,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5214,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5223,12 +5275,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5294,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5330,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5391,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5410,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5446,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5507,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5526,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5562,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5623,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5642,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5678,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5739,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5758,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5794,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5855,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5874,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,7 +5910,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/23</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5923,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5881,7 +5933,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5891,40 +5943,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5938,7 +5994,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5948,33 +6004,37 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5987,52 +6047,56 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6040,7 +6104,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6054,7 +6118,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6064,33 +6128,37 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -6103,60 +6171,64 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6170,7 +6242,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6180,33 +6252,37 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -6219,22 +6295,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6272,7 +6348,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6286,7 +6362,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6322,7 +6398,2119 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD68"/>
+  <dimension ref="A1:AD77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1735,32 +1735,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1768,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1792,33 +1796,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2000,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2232,7 +2240,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2348,7 +2356,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2468,7 +2476,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2588,7 +2596,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2708,7 +2716,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2828,7 +2836,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2944,7 +2952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2998,7 +3006,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3072,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3113,7 +3121,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3184,7 +3192,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3241,70 +3249,66 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3318,7 +3322,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3328,65 +3332,61 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/23</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3463,18 +3463,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3491,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3497,7 +3501,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3540,7 +3544,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3554,7 +3558,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3579,7 +3583,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3590,7 +3594,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3607,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3613,7 +3617,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3623,32 +3627,36 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3656,7 +3664,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3670,7 +3678,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3680,17 +3688,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3700,13 +3708,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3719,22 +3731,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3772,7 +3784,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3786,7 +3798,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3811,7 +3823,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3822,7 +3834,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3835,22 +3847,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3888,7 +3900,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3902,7 +3914,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3938,7 +3950,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3963,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3999,12 +4011,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4018,7 +4030,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4054,7 +4066,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4067,22 +4079,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4115,12 +4127,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4134,7 +4146,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4170,7 +4182,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4183,22 +4195,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4231,12 +4243,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4250,7 +4262,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4286,7 +4298,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4299,22 +4311,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4347,12 +4359,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4366,7 +4378,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4402,7 +4414,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4427,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4425,7 +4437,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4463,12 +4475,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4482,7 +4494,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4518,7 +4530,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4543,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4541,7 +4553,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4579,12 +4591,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4598,7 +4610,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4634,7 +4646,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4659,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4657,7 +4669,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4695,12 +4707,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4714,7 +4726,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4750,7 +4762,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4775,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4773,7 +4785,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4811,12 +4823,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4830,7 +4842,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4866,7 +4878,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4891,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4889,7 +4901,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4927,12 +4939,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4946,7 +4958,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4982,7 +4994,7 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5007,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5005,7 +5017,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5043,12 +5055,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5062,7 +5074,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5098,7 +5110,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5123,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5121,7 +5133,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5159,12 +5171,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5178,7 +5190,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5214,7 +5226,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5239,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5237,7 +5249,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5275,12 +5287,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5294,7 +5306,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5330,7 +5342,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5355,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5353,7 +5365,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5391,12 +5403,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5410,7 +5422,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5446,7 +5458,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5471,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5469,7 +5481,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5507,12 +5519,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5526,7 +5538,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5562,7 +5574,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5587,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5585,7 +5597,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5623,12 +5635,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5642,7 +5654,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5678,7 +5690,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5703,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5701,7 +5713,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5739,12 +5751,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5758,7 +5770,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5794,7 +5806,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5819,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5817,7 +5829,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5860,7 +5872,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5874,7 +5886,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5910,77 +5922,73 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/23</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5994,7 +6002,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6004,99 +6012,91 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6128,107 +6128,99 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6242,7 +6234,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6252,65 +6244,61 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6348,7 +6336,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6362,7 +6350,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6398,35 +6386,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6459,12 +6447,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6478,7 +6466,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6514,77 +6502,73 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6598,7 +6582,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6608,17 +6592,17 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6628,17 +6612,13 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6631,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6661,7 +6641,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6671,40 +6651,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6718,7 +6702,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6728,33 +6712,37 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -6767,60 +6755,64 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6834,7 +6826,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6844,33 +6836,37 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -6883,60 +6879,64 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6960,33 +6960,37 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -6999,7 +7003,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7009,7 +7013,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7047,12 +7051,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7066,7 +7070,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7091,7 +7095,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7115,22 +7119,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7163,12 +7167,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7182,7 +7186,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7207,7 +7211,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7231,60 +7235,64 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>07:32</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7298,7 +7306,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7308,33 +7316,37 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -7347,22 +7359,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7395,12 +7407,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7414,7 +7426,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7463,22 +7475,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7511,12 +7523,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7555,7 +7567,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7579,7 +7591,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7589,7 +7601,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7627,12 +7639,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7646,7 +7658,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7695,22 +7707,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7743,12 +7755,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7787,22 +7799,18 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -7815,22 +7823,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>08:08</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7863,12 +7871,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7882,7 +7890,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7907,7 +7915,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7931,22 +7939,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7979,12 +7987,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7998,7 +8006,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8023,22 +8031,18 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -8051,22 +8055,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8099,12 +8103,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8118,7 +8122,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8143,22 +8147,18 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -8171,22 +8171,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8238,7 +8238,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8379,22 +8379,18 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8403,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8417,7 +8413,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8460,7 +8456,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8474,41 +8470,1101 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>08:33</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr"/>
-      <c r="AD68" s="2" t="inlineStr">
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
         <is>
           <t>—/17</t>
         </is>

--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD77"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,18 +715,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -920,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1083,12 +1087,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1503,32 +1507,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1536,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1560,17 +1568,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1580,13 +1588,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1619,32 +1631,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1652,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1676,17 +1692,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1696,13 +1712,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1745,24 +1765,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1772,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1821,12 +1841,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1879,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1892,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1916,33 +1940,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1975,32 +2003,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2008,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2032,33 +2064,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2091,32 +2127,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2124,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2148,33 +2188,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2207,32 +2251,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2240,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2264,33 +2312,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2375,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2356,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,37 +2436,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2530,7 +2586,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2563,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2596,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2620,27 +2680,27 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2716,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2836,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2952,7 +3012,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3192,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3236,13 +3296,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3352,13 +3416,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3492,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3473,40 +3541,40 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3539,12 +3607,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3558,7 +3626,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3588,83 +3656,83 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3678,7 +3746,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3688,65 +3756,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3779,12 +3847,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3798,7 +3866,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3828,41 +3896,45 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3895,12 +3967,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3914,7 +3986,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3939,46 +4011,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4011,12 +4087,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4030,7 +4106,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4055,46 +4131,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4127,12 +4207,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4146,7 +4226,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4171,18 +4251,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4279,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4205,7 +4289,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4243,12 +4327,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4262,7 +4346,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4287,7 +4371,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4311,7 +4395,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4321,7 +4405,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4331,40 +4415,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4378,7 +4466,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4388,33 +4476,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -4427,60 +4519,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4494,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4504,33 +4600,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4643,32 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4591,12 +4691,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4604,13 +4704,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4635,7 +4751,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4659,7 +4775,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4669,7 +4785,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4679,40 +4795,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4726,7 +4846,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4736,33 +4856,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4899,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4785,7 +4909,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4795,40 +4919,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4842,7 +4970,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4852,33 +4980,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -4891,22 +5023,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4939,12 +5071,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4958,7 +5090,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5007,60 +5139,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5074,7 +5210,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5084,33 +5220,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5263,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5133,7 +5273,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5176,7 +5316,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5190,7 +5330,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5215,7 +5355,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5239,7 +5379,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5249,7 +5389,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5287,12 +5427,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5306,7 +5446,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5355,7 +5495,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5365,7 +5505,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5403,12 +5543,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5422,7 +5562,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5471,7 +5611,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5481,7 +5621,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5519,12 +5659,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5538,7 +5678,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5587,7 +5727,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5597,7 +5737,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5635,12 +5775,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5654,7 +5794,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5703,7 +5843,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5713,7 +5853,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5751,12 +5891,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5770,7 +5910,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5819,7 +5959,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5829,7 +5969,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5867,12 +6007,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5886,7 +6026,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5935,7 +6075,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5945,7 +6085,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5983,12 +6123,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6002,7 +6142,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6051,7 +6191,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6061,7 +6201,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6099,12 +6239,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6118,7 +6258,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6167,7 +6307,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6177,7 +6317,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6220,7 +6360,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6234,7 +6374,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6283,7 +6423,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6293,7 +6433,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6331,12 +6471,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6350,7 +6490,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6375,7 +6515,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6399,7 +6539,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6409,7 +6549,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6452,7 +6592,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6466,7 +6606,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6515,7 +6655,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6525,7 +6665,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6568,7 +6708,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6582,7 +6722,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6607,7 +6747,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6625,70 +6765,66 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6702,7 +6838,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6712,99 +6848,91 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6812,7 +6940,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6826,7 +6954,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6836,107 +6964,99 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6950,7 +7070,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6960,65 +7080,61 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7056,7 +7172,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7070,7 +7186,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7095,7 +7211,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7106,35 +7222,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7167,12 +7283,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7186,7 +7302,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7222,77 +7338,73 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7306,7 +7418,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7316,17 +7428,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7341,40 +7453,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7407,12 +7519,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7426,7 +7538,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7451,46 +7563,50 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7523,12 +7639,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7542,7 +7658,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7578,35 +7694,35 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7639,12 +7755,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7658,7 +7774,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7683,46 +7799,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7755,12 +7875,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7774,7 +7894,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7799,46 +7919,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7871,12 +7995,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7890,7 +8014,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7920,41 +8044,45 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7987,12 +8115,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8006,7 +8134,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8031,7 +8159,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8042,7 +8170,7 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -8055,52 +8183,56 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8108,7 +8240,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8122,7 +8254,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8132,33 +8264,37 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8307,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8181,7 +8317,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8191,40 +8327,44 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8238,7 +8378,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8248,33 +8388,37 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -8287,60 +8431,64 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8354,7 +8502,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8364,33 +8512,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -8403,22 +8555,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8456,7 +8608,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8470,7 +8622,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8495,22 +8647,18 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8671,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8533,7 +8681,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8571,12 +8719,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8590,7 +8738,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8615,7 +8763,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8639,7 +8787,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8649,7 +8797,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8659,40 +8807,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8706,7 +8858,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8716,17 +8868,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8741,12 +8893,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8911,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8769,7 +8921,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8812,7 +8964,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8826,7 +8978,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8856,17 +9008,13 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -8879,7 +9027,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8889,7 +9037,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8899,40 +9047,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8946,7 +9098,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8956,33 +9108,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9151,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9005,7 +9161,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9015,40 +9171,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9062,7 +9222,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9072,17 +9232,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9097,12 +9257,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -9115,60 +9275,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9182,7 +9346,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9192,17 +9356,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9212,13 +9376,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9399,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9241,7 +9409,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9251,40 +9419,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9298,7 +9470,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9308,17 +9480,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9328,13 +9500,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9523,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9357,7 +9533,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9395,12 +9571,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9414,7 +9590,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9439,7 +9615,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9463,60 +9639,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9530,7 +9710,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9540,31 +9720,2515 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC77" s="2" t="inlineStr"/>
-      <c r="AD77" s="2" t="inlineStr">
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
         <is>
           <t>—/17</t>
         </is>

--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD159"/>
+  <dimension ref="A1:AD161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2332,17 +2332,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4064,17 +4064,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5229,24 +5229,24 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5467,32 +5467,36 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5524,17 +5528,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5544,12 +5548,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5587,32 +5591,36 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5620,7 +5628,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5644,17 +5652,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5664,17 +5672,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5860,7 +5868,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5980,7 +5988,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6100,7 +6108,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6220,7 +6228,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6274,7 +6282,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6348,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6394,7 +6402,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6468,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6514,7 +6522,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6588,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6624,17 +6632,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6708,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6754,7 +6762,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7076,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7568,7 +7576,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7692,7 +7700,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -8056,7 +8064,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8296,7 +8304,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8345,7 +8353,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8416,7 +8424,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8465,7 +8473,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8540,7 +8548,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8660,7 +8668,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,7 +8784,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8896,7 +8904,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9020,7 +9028,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9059,7 +9067,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -9392,7 +9400,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,7 +9524,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9640,7 +9648,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -10120,7 +10128,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10624,7 +10632,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10748,7 +10756,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -11244,7 +11252,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11341,24 +11349,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -11368,7 +11376,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11417,7 +11425,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11465,24 +11473,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -11492,7 +11500,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11541,7 +11549,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11612,7 +11620,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11732,7 +11740,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11848,7 +11856,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11964,7 +11972,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12084,7 +12092,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12123,7 +12131,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -12204,7 +12212,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12324,7 +12332,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12444,7 +12452,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12564,7 +12572,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12804,7 +12812,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12924,7 +12932,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13044,7 +13052,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13160,7 +13168,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13276,7 +13284,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13396,7 +13404,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13512,7 +13520,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13573,70 +13581,66 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13650,7 +13654,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13660,17 +13664,17 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr">
@@ -13680,17 +13684,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -13703,7 +13707,7 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -13713,7 +13717,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -13733,24 +13737,24 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -13760,7 +13764,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13774,7 +13778,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13799,22 +13803,22 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -13827,24 +13831,24 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -13857,19 +13861,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -13879,12 +13883,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13898,7 +13902,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13928,17 +13932,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -13951,60 +13955,64 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14028,27 +14036,27 @@
       </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z111" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA111" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
@@ -14071,7 +14079,7 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14081,7 +14089,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -14119,12 +14127,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14138,7 +14146,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -14163,18 +14171,22 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC112" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -14187,64 +14199,60 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14268,37 +14276,33 @@
       </c>
       <c r="X113" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z113" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA113" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC113" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr"/>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -14311,52 +14315,56 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N114" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -14364,7 +14372,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14378,7 +14386,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -14388,22 +14396,22 @@
       </c>
       <c r="X114" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z114" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
@@ -14413,12 +14421,12 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -14431,56 +14439,52 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -14488,7 +14492,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14502,7 +14506,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -14512,37 +14516,37 @@
       </c>
       <c r="X115" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z115" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA115" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -14555,24 +14559,24 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -14585,34 +14589,34 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14626,7 +14630,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -14651,22 +14655,22 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB116" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14683,7 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -14689,7 +14693,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -14709,34 +14713,34 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14750,7 +14754,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14775,22 +14779,22 @@
       </c>
       <c r="AA117" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -14803,24 +14807,24 @@
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -14833,12 +14837,12 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -14855,12 +14859,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14899,22 +14903,22 @@
       </c>
       <c r="AA118" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB118" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -14927,60 +14931,64 @@
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>07:32</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14994,7 +15002,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -15004,33 +15012,37 @@
       </c>
       <c r="X119" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z119" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC119" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -15043,64 +15055,60 @@
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N120" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15114,7 +15122,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -15124,37 +15132,33 @@
       </c>
       <c r="X120" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z120" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC120" s="2" t="inlineStr">
-        <is>
-          <t>87.7</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -15167,60 +15171,64 @@
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15234,7 +15242,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -15244,17 +15252,17 @@
       </c>
       <c r="X121" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z121" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA121" s="2" t="inlineStr">
@@ -15264,17 +15272,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -15287,7 +15295,7 @@
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -15297,7 +15305,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15335,12 +15343,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15354,7 +15362,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -15379,22 +15387,22 @@
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB122" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -15407,64 +15415,60 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15478,7 +15482,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -15488,37 +15492,37 @@
       </c>
       <c r="X123" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z123" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -15531,60 +15535,64 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>08:08</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15598,7 +15606,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -15608,33 +15616,37 @@
       </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z124" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA124" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC124" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC124" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -15647,22 +15659,22 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>08:11</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -15695,12 +15707,12 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15714,7 +15726,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -15739,22 +15751,18 @@
       </c>
       <c r="AA125" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC125" s="2" t="inlineStr">
-        <is>
-          <t>88.3</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr"/>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -15767,22 +15775,22 @@
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15815,12 +15823,12 @@
       <c r="N126" s="2" t="inlineStr"/>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15834,7 +15842,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15864,17 +15872,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -15887,7 +15895,7 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -15897,7 +15905,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15940,7 +15948,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -15954,7 +15962,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -15979,22 +15987,22 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -16007,64 +16015,60 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N128" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16078,7 +16082,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -16088,22 +16092,22 @@
       </c>
       <c r="X128" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z128" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
@@ -16113,12 +16117,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16135,7 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -16141,7 +16145,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16161,7 +16165,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -16173,22 +16177,22 @@
       <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16202,7 +16206,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -16227,7 +16231,7 @@
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
@@ -16255,60 +16259,64 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N130" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16322,7 +16330,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -16332,37 +16340,37 @@
       </c>
       <c r="X130" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y130" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z130" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA130" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -16375,56 +16383,52 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N131" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -16432,7 +16436,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16446,7 +16450,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -16456,37 +16460,37 @@
       </c>
       <c r="X131" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y131" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z131" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA131" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16503,7 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -16519,40 +16523,44 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16576,33 +16584,37 @@
       </c>
       <c r="X132" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y132" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z132" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA132" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC132" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16627,7 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -16625,7 +16637,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -16635,44 +16647,40 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N133" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr"/>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16686,7 +16694,7 @@
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
@@ -16696,17 +16704,17 @@
       </c>
       <c r="X133" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y133" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z133" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA133" s="2" t="inlineStr">
@@ -16716,17 +16724,13 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC133" s="2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC133" s="2" t="inlineStr"/>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -16739,24 +16743,24 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16769,24 +16773,24 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -16796,7 +16800,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16835,7 +16839,7 @@
       </c>
       <c r="AA134" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB134" s="2" t="inlineStr">
@@ -16845,12 +16849,12 @@
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -16863,24 +16867,24 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16893,34 +16897,34 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -16934,7 +16938,7 @@
       <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
@@ -16959,22 +16963,22 @@
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -16987,24 +16991,24 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17017,34 +17021,34 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17058,7 +17062,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -17093,12 +17097,12 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -17111,24 +17115,24 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17141,34 +17145,34 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17182,7 +17186,7 @@
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
@@ -17212,17 +17216,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -17235,24 +17239,24 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17265,34 +17269,34 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17306,7 +17310,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -17336,17 +17340,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -17359,24 +17363,24 @@
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17389,34 +17393,34 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17430,7 +17434,7 @@
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
@@ -17455,22 +17459,22 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -17483,60 +17487,64 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N140" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17550,7 +17558,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -17560,22 +17568,22 @@
       </c>
       <c r="X140" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y140" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z140" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA140" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB140" s="2" t="inlineStr">
@@ -17585,12 +17593,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -17603,22 +17611,22 @@
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -17651,12 +17659,12 @@
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17695,7 +17703,7 @@
       </c>
       <c r="AA141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB141" s="2" t="inlineStr">
@@ -17705,12 +17713,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -17723,7 +17731,7 @@
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -17733,7 +17741,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -17743,36 +17751,32 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N142" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr"/>
       <c r="O142" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -17780,7 +17784,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -17794,7 +17798,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -17804,37 +17808,37 @@
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y142" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z142" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA142" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -17847,52 +17851,56 @@
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N143" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -17900,7 +17908,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -17914,7 +17922,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -17924,37 +17932,37 @@
       </c>
       <c r="X143" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y143" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z143" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -17967,22 +17975,22 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -18015,12 +18023,12 @@
       <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18059,22 +18067,22 @@
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18095,7 @@
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -18097,7 +18105,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -18107,44 +18115,40 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18158,7 +18162,7 @@
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
@@ -18168,22 +18172,22 @@
       </c>
       <c r="X145" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y145" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z145" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA145" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB145" s="2" t="inlineStr">
@@ -18193,12 +18197,12 @@
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -18211,24 +18215,24 @@
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18241,34 +18245,34 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18282,7 +18286,7 @@
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
@@ -18307,22 +18311,22 @@
       </c>
       <c r="AA146" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -18335,24 +18339,24 @@
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18365,34 +18369,34 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18406,7 +18410,7 @@
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
@@ -18441,12 +18445,12 @@
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -18459,24 +18463,24 @@
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18489,12 +18493,12 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
@@ -18511,12 +18515,12 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18530,7 +18534,7 @@
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
@@ -18560,17 +18564,17 @@
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -18583,24 +18587,24 @@
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18618,7 +18622,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
@@ -18635,12 +18639,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18654,7 +18658,7 @@
       <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
@@ -18684,17 +18688,17 @@
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -18707,60 +18711,64 @@
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N150" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -18774,7 +18782,7 @@
       <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
@@ -18784,17 +18792,17 @@
       </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z150" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA150" s="2" t="inlineStr">
@@ -18804,17 +18812,17 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -18827,22 +18835,22 @@
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -18875,12 +18883,12 @@
       <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -18894,7 +18902,7 @@
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
@@ -18919,12 +18927,12 @@
       </c>
       <c r="AA151" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
@@ -18947,22 +18955,22 @@
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18995,12 +19003,12 @@
       <c r="N152" s="2" t="inlineStr"/>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19014,7 +19022,7 @@
       <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W152" s="2" t="inlineStr">
@@ -19039,12 +19047,12 @@
       </c>
       <c r="AA152" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
@@ -19067,7 +19075,7 @@
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -19120,7 +19128,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19169,12 +19177,12 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -19187,22 +19195,22 @@
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -19240,7 +19248,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19254,7 +19262,7 @@
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
@@ -19279,22 +19287,22 @@
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -19307,22 +19315,22 @@
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -19355,12 +19363,12 @@
       <c r="N155" s="2" t="inlineStr"/>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19374,7 +19382,7 @@
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W155" s="2" t="inlineStr">
@@ -19399,22 +19407,22 @@
       </c>
       <c r="AA155" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19435,7 @@
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -19475,12 +19483,12 @@
       <c r="N156" s="2" t="inlineStr"/>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19519,7 +19527,7 @@
       </c>
       <c r="AA156" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB156" s="2" t="inlineStr">
@@ -19529,12 +19537,12 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -19547,22 +19555,22 @@
       <c r="B157" s="2" t="inlineStr"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -19595,12 +19603,12 @@
       <c r="N157" s="2" t="inlineStr"/>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19614,7 +19622,7 @@
       <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="W157" s="2" t="inlineStr">
@@ -19639,22 +19647,22 @@
       </c>
       <c r="AA157" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -19667,22 +19675,22 @@
       <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -19715,12 +19723,12 @@
       <c r="N158" s="2" t="inlineStr"/>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19734,7 +19742,7 @@
       <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
@@ -19769,12 +19777,12 @@
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -19787,22 +19795,22 @@
       <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -19835,12 +19843,12 @@
       <c r="N159" s="2" t="inlineStr"/>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -19854,47 +19862,287 @@
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr">
         <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB159" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC159" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AD159" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="W159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X159" s="2" t="inlineStr">
+      <c r="X160" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y159" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z159" s="2" t="inlineStr">
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z160" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA159" s="2" t="inlineStr">
+      <c r="AA160" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB159" s="2" t="inlineStr">
+      <c r="AB160" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC159" s="2" t="inlineStr">
+      <c r="AC160" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="AD159" s="2" t="inlineStr">
+      <c r="AD160" s="2" t="inlineStr">
         <is>
           <t>12/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB161" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC161" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AD161" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-operations.xlsx
+++ b/data/export/2026-10-19-operations.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,17 +8148,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,17 +8272,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9636,17 +9636,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10256,17 +10256,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10380,17 +10380,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10996,17 +10996,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11368,17 +11368,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11659,32 +11659,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11692,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11736,17 +11740,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11783,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11812,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11836,17 +11844,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11856,12 +11864,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11899,32 +11907,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11932,7 +11944,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11956,17 +11968,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11976,17 +11988,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12019,32 +12031,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12052,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12076,17 +12092,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12096,17 +12112,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12139,32 +12155,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12172,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12196,17 +12216,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12216,17 +12236,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12312,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12346,7 +12366,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12432,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12456,17 +12476,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12606,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12730,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12854,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13056,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13090,7 +13110,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13234,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13478,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13544,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13578,7 +13598,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13668,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13692,17 +13712,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13842,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13908,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13942,7 +13962,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14028,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14062,7 +14082,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14148,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14172,17 +14192,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14326,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14392,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14416,17 +14436,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14512,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14616,7 +14636,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14670,7 +14690,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14760,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14789,12 +14809,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14884,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14908,12 +14928,12 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15042,7 +15062,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15132,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15166,7 +15186,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15310,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15380,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15414,7 +15434,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15500,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15524,17 +15544,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15678,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15798,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15918,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16120,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16154,7 +16174,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16298,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16422,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16546,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16616,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16650,7 +16670,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16740,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16764,17 +16784,17 @@
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -16844,7 +16864,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16898,7 +16918,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17042,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17112,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17146,7 +17166,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17236,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17260,17 +17280,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17414,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17484,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17508,17 +17528,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17608,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17712,7 +17732,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17766,7 +17786,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17856,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17885,12 +17905,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -17960,7 +17980,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18014,7 +18034,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18158,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -18208,7 +18228,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18262,7 +18282,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18406,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -18506,7 +18526,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -18630,7 +18650,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18774,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -18820,7 +18840,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -19134,7 +19154,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -19204,7 +19224,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19258,7 +19278,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -19382,7 +19402,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19472,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19496,17 +19516,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19596,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19625,12 +19645,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19720,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19754,7 +19774,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19894,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -19998,7 +20018,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20142,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -20246,7 +20266,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20390,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20440,7 +20460,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20484,17 +20504,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -20816,7 +20836,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20870,7 +20890,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20956,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21056,7 +21076,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21100,12 +21120,12 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
@@ -21180,7 +21200,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21234,7 +21254,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -21300,7 +21320,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21344,17 +21364,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21444,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21468,17 +21488,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -21548,7 +21568,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21602,7 +21622,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21692,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21726,7 +21746,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -21796,7 +21816,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21850,7 +21870,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21974,7 +21994,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22064,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22098,7 +22118,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22188,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22222,7 +22242,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22346,7 +22366,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22470,7 +22490,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22614,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -22718,7 +22738,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22862,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -23028,7 +23048,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23125,24 +23145,24 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O184" s="2" t="inlineStr">
@@ -23152,7 +23172,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23201,12 +23221,12 @@
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -23239,32 +23259,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23272,7 +23296,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23296,17 +23320,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23316,17 +23340,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -23359,32 +23383,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23392,7 +23420,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23416,17 +23444,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -23436,12 +23464,12 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
@@ -23479,32 +23507,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -23512,7 +23544,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23536,17 +23568,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23556,17 +23588,17 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -23599,12 +23631,12 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -23632,7 +23664,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23640,10 +23672,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R188" s="2" t="inlineStr"/>
-      <c r="S188" s="2" t="inlineStr"/>
-      <c r="T188" s="2" t="inlineStr"/>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±2分钟；反向位置物理seq28（站名待映射） ETA 21分钟参与校验</t>
+        </is>
+      </c>
       <c r="V188" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -23686,7 +23734,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -23719,32 +23767,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23752,7 +23804,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23776,17 +23828,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23796,17 +23848,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -23872,7 +23924,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23926,7 +23978,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -23992,7 +24044,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24046,7 +24098,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -24079,12 +24131,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24112,7 +24164,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24120,10 +24172,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24166,7 +24234,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24300,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24286,7 +24354,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -24319,32 +24387,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -24352,7 +24424,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24376,17 +24448,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24396,17 +24468,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -24472,7 +24544,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24526,7 +24598,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -24592,7 +24664,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24646,7 +24718,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -24712,7 +24784,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24766,7 +24838,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24904,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24956,7 +25028,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25000,12 +25072,12 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -25134,7 +25206,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25330,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -25444,7 +25516,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25568,7 +25640,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25622,7 +25694,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25938,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -25936,7 +26008,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -25980,12 +26052,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26184,7 +26256,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26228,17 +26300,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -26482,7 +26554,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26674,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -26668,7 +26740,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26722,7 +26794,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -26792,7 +26864,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26836,12 +26908,12 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -26966,7 +27038,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -27086,7 +27158,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -27206,7 +27278,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -27272,7 +27344,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27326,7 +27398,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -27694,7 +27766,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -27884,7 +27956,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28008,7 +28080,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28052,12 +28124,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28132,7 +28204,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28176,17 +28248,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -28434,7 +28506,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -28558,7 +28630,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28754,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -28752,7 +28824,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28806,7 +28878,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -28992,7 +29064,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29058,7 +29130,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -29182,7 +29254,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -29368,7 +29440,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29424,17 +29496,17 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -29558,7 +29630,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -29806,7 +29878,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -29930,7 +30002,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30126,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -30302,7 +30374,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -30422,7 +30494,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30688,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30660,12 +30732,12 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
@@ -30790,7 +30862,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -31038,7 +31110,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -31162,7 +31234,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -31286,7 +31358,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31428,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31400,12 +31472,12 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
@@ -31658,7 +31730,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -31906,7 +31978,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32342,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -32340,7 +32412,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32460,7 +32532,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32504,12 +32576,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32634,7 +32706,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -32758,7 +32830,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -32828,7 +32900,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32882,7 +32954,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33078,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -33076,7 +33148,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33130,7 +33202,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -33196,7 +33268,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33240,17 +33312,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -33374,7 +33446,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -33742,7 +33814,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -34114,7 +34186,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -34184,7 +34256,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34308,7 +34380,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34352,12 +34424,12 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34486,7 +34558,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -34610,7 +34682,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34752,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34734,7 +34806,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34876,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34858,7 +34930,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -34982,7 +35054,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -35106,7 +35178,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -35172,7 +35244,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35216,17 +35288,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -35350,7 +35422,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35616,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35588,12 +35660,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35970,7 +36042,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36112,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36164,7 +36236,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36218,7 +36290,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -36251,36 +36323,32 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr"/>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N291" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr"/>
       <c r="O291" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -36288,7 +36356,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36312,17 +36380,17 @@
       </c>
       <c r="X291" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA291" s="2" t="inlineStr">
@@ -36332,12 +36400,12 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
@@ -36375,32 +36443,36 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr"/>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N292" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O292" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -36408,7 +36480,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36432,17 +36504,17 @@
       </c>
       <c r="X292" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA292" s="2" t="inlineStr">
@@ -36452,17 +36524,17 @@
       </c>
       <c r="AB292" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36600,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36582,7 +36654,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -36615,32 +36687,36 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N294" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -36648,7 +36724,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36672,17 +36748,17 @@
       </c>
       <c r="X294" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA294" s="2" t="inlineStr">
@@ -36692,12 +36768,12 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
@@ -36768,7 +36844,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36888,7 +36964,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36932,12 +37008,12 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37008,7 +37084,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37062,7 +37138,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
